--- a/reports/lab4/chart.xlsx
+++ b/reports/lab4/chart.xlsx
@@ -1103,11 +1103,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="33273225"/>
-        <c:axId val="83200433"/>
+        <c:axId val="19302738"/>
+        <c:axId val="17007782"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="33273225"/>
+        <c:axId val="19302738"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1172,7 +1172,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83200433"/>
+        <c:crossAx val="17007782"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1180,7 +1180,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83200433"/>
+        <c:axId val="17007782"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1254,7 +1254,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33273225"/>
+        <c:crossAx val="19302738"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1836,11 +1836,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="42911058"/>
-        <c:axId val="98891636"/>
+        <c:axId val="57348433"/>
+        <c:axId val="42524800"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="42911058"/>
+        <c:axId val="57348433"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1905,7 +1905,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98891636"/>
+        <c:crossAx val="42524800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1913,7 +1913,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="98891636"/>
+        <c:axId val="42524800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1987,7 +1987,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42911058"/>
+        <c:crossAx val="57348433"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2050,9 +2050,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1909800</xdr:colOff>
+      <xdr:colOff>1909440</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>149040</xdr:rowOff>
+      <xdr:rowOff>148680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2061,7 +2061,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="523440" y="1769760"/>
-        <a:ext cx="7415640" cy="4170600"/>
+        <a:ext cx="7416000" cy="4170240"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2080,9 +2080,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>581400</xdr:colOff>
+      <xdr:colOff>581040</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>75240</xdr:rowOff>
+      <xdr:rowOff>74880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2090,8 +2090,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8614080" y="1695960"/>
-        <a:ext cx="7415640" cy="4170600"/>
+        <a:off x="8614800" y="1695960"/>
+        <a:ext cx="7415640" cy="4170240"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2300,7 +2300,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="29.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="27.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="10.16"/>
   </cols>
   <sheetData>
